--- a/DATA/Injections.xlsx
+++ b/DATA/Injections.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/072b28d6aeebde12/Performances/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mon Drive\Performances\performApp\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05691530-905D-4168-BE64-6D755AD7B4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE36617-5206-4967-83FD-CF6B3F43FB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{0D33AA1F-2F2B-44CA-84CF-012614ECCD38}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0D33AA1F-2F2B-44CA-84CF-012614ECCD38}"/>
   </bookViews>
   <sheets>
     <sheet name="Injection" sheetId="1" r:id="rId1"/>
@@ -25,16 +25,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>1 jour de retard</t>
+  </si>
+  <si>
+    <t>2 jour de retard</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -42,50 +48,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -94,9 +71,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,11 +388,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C2225A3-D882-4174-B178-D0628ACD8D39}">
-  <dimension ref="A1:A174"/>
+  <dimension ref="A1:B174"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
@@ -638,411 +615,458 @@
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="3"/>
+      <c r="A40" s="2">
+        <v>45741</v>
+      </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="3"/>
+      <c r="A41" s="2">
+        <v>45762</v>
+      </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="3"/>
+      <c r="A42" s="2">
+        <v>45783</v>
+      </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="3"/>
+      <c r="A43" s="2">
+        <v>45804</v>
+      </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="3"/>
+      <c r="A44" s="2">
+        <v>45825</v>
+      </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="3"/>
+      <c r="A45" s="2">
+        <v>45846</v>
+      </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="3"/>
+      <c r="A46" s="2">
+        <v>45867</v>
+      </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="3"/>
+      <c r="A47" s="2">
+        <v>45888</v>
+      </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="3"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="3"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="3"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="3"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="3"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="3"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="3"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="3"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="3"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="3"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="3"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="3"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="3"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="3"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="3"/>
+      <c r="A48" s="2">
+        <v>45909</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>45951</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>45993</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>46014</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>46077</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B57" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="1"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="1"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="1"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="1"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="1"/>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="3"/>
+      <c r="A65" s="1"/>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="3"/>
+      <c r="A66" s="1"/>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="3"/>
+      <c r="A67" s="1"/>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="3"/>
+      <c r="A68" s="1"/>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="3"/>
+      <c r="A69" s="1"/>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="3"/>
+      <c r="A70" s="1"/>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="3"/>
+      <c r="A71" s="1"/>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="3"/>
+      <c r="A72" s="1"/>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="3"/>
+      <c r="A73" s="1"/>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="3"/>
+      <c r="A74" s="1"/>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="3"/>
+      <c r="A75" s="1"/>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="3"/>
+      <c r="A76" s="1"/>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="3"/>
+      <c r="A77" s="1"/>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="3"/>
+      <c r="A78" s="1"/>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="3"/>
+      <c r="A79" s="1"/>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="3"/>
+      <c r="A80" s="1"/>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="3"/>
+      <c r="A81" s="1"/>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="3"/>
+      <c r="A82" s="1"/>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="3"/>
+      <c r="A83" s="1"/>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="3"/>
+      <c r="A84" s="1"/>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="3"/>
+      <c r="A85" s="1"/>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="3"/>
+      <c r="A86" s="1"/>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="3"/>
+      <c r="A87" s="1"/>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="3"/>
+      <c r="A88" s="1"/>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="3"/>
+      <c r="A89" s="1"/>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="3"/>
+      <c r="A90" s="1"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="3"/>
+      <c r="A91" s="1"/>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="3"/>
+      <c r="A92" s="1"/>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="3"/>
+      <c r="A93" s="1"/>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="3"/>
+      <c r="A94" s="1"/>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="3"/>
+      <c r="A95" s="1"/>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="3"/>
+      <c r="A96" s="1"/>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="3"/>
+      <c r="A97" s="1"/>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="3"/>
+      <c r="A98" s="1"/>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="3"/>
+      <c r="A99" s="1"/>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="3"/>
+      <c r="A100" s="1"/>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="3"/>
+      <c r="A101" s="1"/>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" s="3"/>
+      <c r="A102" s="1"/>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" s="3"/>
+      <c r="A103" s="1"/>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" s="3"/>
+      <c r="A104" s="1"/>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" s="3"/>
+      <c r="A105" s="1"/>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" s="3"/>
+      <c r="A106" s="1"/>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" s="3"/>
+      <c r="A107" s="1"/>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" s="3"/>
+      <c r="A108" s="1"/>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" s="3"/>
+      <c r="A109" s="1"/>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" s="3"/>
+      <c r="A110" s="1"/>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" s="3"/>
+      <c r="A111" s="1"/>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" s="3"/>
+      <c r="A112" s="1"/>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" s="3"/>
+      <c r="A113" s="1"/>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" s="3"/>
+      <c r="A114" s="1"/>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" s="3"/>
+      <c r="A115" s="1"/>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" s="3"/>
+      <c r="A116" s="1"/>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" s="3"/>
+      <c r="A117" s="1"/>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" s="3"/>
+      <c r="A118" s="1"/>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" s="3"/>
+      <c r="A119" s="1"/>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" s="3"/>
+      <c r="A120" s="1"/>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" s="3"/>
+      <c r="A121" s="1"/>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" s="3"/>
+      <c r="A122" s="1"/>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" s="3"/>
+      <c r="A123" s="1"/>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" s="3"/>
+      <c r="A124" s="1"/>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" s="3"/>
+      <c r="A125" s="1"/>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" s="3"/>
+      <c r="A126" s="1"/>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" s="3"/>
+      <c r="A127" s="1"/>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" s="3"/>
+      <c r="A128" s="1"/>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" s="3"/>
+      <c r="A129" s="1"/>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" s="3"/>
+      <c r="A130" s="1"/>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="3"/>
+      <c r="A131" s="1"/>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" s="3"/>
+      <c r="A132" s="1"/>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" s="3"/>
+      <c r="A133" s="1"/>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" s="3"/>
+      <c r="A134" s="1"/>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" s="3"/>
+      <c r="A135" s="1"/>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A136" s="3"/>
+      <c r="A136" s="1"/>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" s="3"/>
+      <c r="A137" s="1"/>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" s="3"/>
+      <c r="A138" s="1"/>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" s="3"/>
+      <c r="A139" s="1"/>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A140" s="3"/>
+      <c r="A140" s="1"/>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A141" s="3"/>
+      <c r="A141" s="1"/>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A142" s="3"/>
+      <c r="A142" s="1"/>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A143" s="3"/>
+      <c r="A143" s="1"/>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A144" s="3"/>
+      <c r="A144" s="1"/>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A145" s="3"/>
+      <c r="A145" s="1"/>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A146" s="3"/>
+      <c r="A146" s="1"/>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A147" s="3"/>
+      <c r="A147" s="1"/>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A148" s="3"/>
+      <c r="A148" s="1"/>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A149" s="3"/>
+      <c r="A149" s="1"/>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" s="3"/>
+      <c r="A150" s="1"/>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A151" s="3"/>
+      <c r="A151" s="1"/>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A152" s="3"/>
+      <c r="A152" s="1"/>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A153" s="3"/>
+      <c r="A153" s="1"/>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A154" s="3"/>
+      <c r="A154" s="1"/>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A155" s="3"/>
+      <c r="A155" s="1"/>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A156" s="3"/>
+      <c r="A156" s="1"/>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A157" s="3"/>
+      <c r="A157" s="1"/>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A158" s="3"/>
+      <c r="A158" s="1"/>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A159" s="3"/>
+      <c r="A159" s="1"/>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A160" s="3"/>
+      <c r="A160" s="1"/>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A161" s="3"/>
+      <c r="A161" s="1"/>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A162" s="3"/>
+      <c r="A162" s="1"/>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A163" s="3"/>
+      <c r="A163" s="1"/>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A164" s="3"/>
+      <c r="A164" s="1"/>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A165" s="3"/>
+      <c r="A165" s="1"/>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A166" s="3"/>
+      <c r="A166" s="1"/>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A167" s="3"/>
+      <c r="A167" s="1"/>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A168" s="3"/>
+      <c r="A168" s="1"/>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A169" s="3"/>
+      <c r="A169" s="1"/>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A170" s="3"/>
+      <c r="A170" s="1"/>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A171" s="3"/>
+      <c r="A171" s="1"/>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A172" s="3"/>
+      <c r="A172" s="1"/>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A173" s="3"/>
+      <c r="A173" s="1"/>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A174" s="3"/>
+      <c r="A174" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>